--- a/courseware/calendario.xlsx
+++ b/courseware/calendario.xlsx
@@ -1,27 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\tiago\insper\alglin\courseware\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17666FAF-DB3E-440A-BE39-A0B23B840E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34452" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Calendario" sheetId="1" r:id="rId1"/>
-    <sheet name="Instruções" sheetId="2" r:id="rId2"/>
+    <sheet r:id="rId1" sheetId="1" name="Calendario"/>
+    <sheet r:id="rId2" sheetId="2" name="Instruções"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="87">
   <si>
     <t>Como preencher esta planilha:</t>
   </si>
@@ -29,7 +23,16 @@
     <t>- Data: data da aula/atividade (uma linha por item de calendário).</t>
   </si>
   <si>
-    <t>- Atividade: texto livre exibido no calendário (ex.: "Teoria: Determinantes").</t>
+    <t>- Conteúdo: o "Fundamentos / Conteúdo" da aula — texto curto, usado como</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  título do item no calendário (e como texto do link, se houver).</t>
+  </si>
+  <si>
+    <t>- Questão: a "Questão / Problema / Desafio" da aula — frase mais longa,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  exibida como subtítulo abaixo do conteúdo.</t>
   </si>
   <si>
     <t>- Link: caminho relativo à pasta courseware/docs/ do arquivo correspondente</t>
@@ -38,7 +41,7 @@
     <t xml:space="preserve">  (o mesmo formato usado no nav: do mkdocs.yml), ex.: matrizes/determinante.md.</t>
   </si>
   <si>
-    <t xml:space="preserve">  Pode ficar em branco quando não há material associado (ex.: avaliações).</t>
+    <t xml:space="preserve">  Pode ficar em branco quando não há material associado (ex.: testes e avaliações).</t>
   </si>
   <si>
     <t>Depois de editar e salvar este arquivo, rode `mkdocs serve -f courseware/mkdocs.yml`</t>
@@ -53,42 +56,234 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Atividade</t>
+    <t>Conteúdo</t>
+  </si>
+  <si>
+    <t>Questão</t>
   </si>
   <si>
     <t>Link</t>
   </si>
   <si>
-    <t>Teoria: Uma caminhada por Chicago</t>
+    <t>Vetores. Soma de vetores. Multiplicação de vetores por escalares.</t>
+  </si>
+  <si>
+    <t>Usar vetores como uma ferramenta matemática para modelar situações da vida real.</t>
   </si>
   <si>
     <t>vetores/caminhando_pela_cidade.ipynb</t>
   </si>
   <si>
-    <t>Teoria: Propriedades de vetores</t>
+    <t>Vetores. Soma de vetores. Multiplicação de vetores por escalares. Técnicas de demonstração.</t>
+  </si>
+  <si>
+    <t>Entender propriedades de vetores e como elas se aplicam em situações problema.</t>
   </si>
   <si>
     <t>vetores/propriedades_soma_e_multiplicacao_escalar.md</t>
   </si>
   <si>
-    <t>Exercícios: Vetores (Parte 1)</t>
-  </si>
-  <si>
-    <t>exercicios/vetores_parte1.md</t>
-  </si>
-  <si>
-    <t>Avaliação: Teste 1</t>
-  </si>
-  <si>
-    <t>Teste</t>
+    <t>Ângulos e distâncias entre vetores. Forma polar. Técnicas de demonstração.</t>
+  </si>
+  <si>
+    <t>Deduzir propriedades relacionadas a ângulos e distâncias em vetores de duas dimensões.</t>
+  </si>
+  <si>
+    <t>vetores/angulos.ipynb</t>
+  </si>
+  <si>
+    <t>Teste 1</t>
+  </si>
+  <si>
+    <t>Numpy.</t>
+  </si>
+  <si>
+    <t>Usar Numpy para representar vetores e suas</t>
+  </si>
+  <si>
+    <t>vetores/numpy01.ipynb</t>
+  </si>
+  <si>
+    <t>Numpy como ferramenta para visualizar</t>
+  </si>
+  <si>
+    <t>Aplicar Numpy e álgebra vetorial para simular uma situação-problema.</t>
+  </si>
+  <si>
+    <t>vetores/confetes.md</t>
+  </si>
+  <si>
+    <t>Produto interno e projeções.</t>
+  </si>
+  <si>
+    <t>Entender o conceito de projeções e de produto interno, relacionando-as com o ângulo entre vetores.</t>
+  </si>
+  <si>
+    <t>vetores/projecoes.ipynb</t>
+  </si>
+  <si>
+    <t>Embeddings</t>
+  </si>
+  <si>
+    <t>Aplicar Numpy para visualizar espaços de embeddings e suas propriedades.</t>
+  </si>
+  <si>
+    <t>vetores/busca_embeddings.md</t>
+  </si>
+  <si>
+    <t>Matrizes. Matrizes transpostas.</t>
+  </si>
+  <si>
+    <t>Representar dados em matrizes.</t>
+  </si>
+  <si>
+    <t>matrizes/matrizes.md</t>
+  </si>
+  <si>
+    <t>Sistemas lineares. Sistemas dinâmicos.</t>
+  </si>
+  <si>
+    <t>Representar sistemas em matrizes.</t>
+  </si>
+  <si>
+    <t>matrizes/sistemas_carcaras.md</t>
+  </si>
+  <si>
+    <t>Matriz inversa. Solução de sistemas lineares.</t>
+  </si>
+  <si>
+    <t>Solucionar um sistema representado como uma matriz.</t>
+  </si>
+  <si>
+    <t>matrizes/inversa.md</t>
+  </si>
+  <si>
+    <t>Determinantes</t>
+  </si>
+  <si>
+    <t>Determinar se um sistema linear tem solução ou não.</t>
+  </si>
+  <si>
+    <t>matrizes/determinante.md</t>
+  </si>
+  <si>
+    <t>Transformações afins</t>
+  </si>
+  <si>
+    <t>Relacionar sistemas lineares com transformações geométricas.</t>
+  </si>
+  <si>
+    <t>matrizes/pratica_afins.ipynb</t>
+  </si>
+  <si>
+    <t>Teste 2</t>
+  </si>
+  <si>
+    <t>Revisão</t>
+  </si>
+  <si>
+    <t>matrizes/revisao.md</t>
+  </si>
+  <si>
+    <t>Avaliação Intermediária</t>
+  </si>
+  <si>
+    <t>Mudanças de Base</t>
+  </si>
+  <si>
+    <t>Entender o que é uma "base".</t>
+  </si>
+  <si>
+    <t>avancado/bases.ipynb</t>
+  </si>
+  <si>
+    <t>Mudanças de Base em Cores de Pixels</t>
+  </si>
+  <si>
+    <t>Aplicar mudanças de base em vetores de pixels.</t>
+  </si>
+  <si>
+    <t>avancado/pixels.ipynb</t>
+  </si>
+  <si>
+    <t>Auto-valores e auto-vetores</t>
+  </si>
+  <si>
+    <t>Entender como auto-valores e auto-vetores permitem entender características de um sistema dinâmico.</t>
+  </si>
+  <si>
+    <t>avancado/autovetores_autovalores.md</t>
+  </si>
+  <si>
+    <t>Cadeias de Markov</t>
+  </si>
+  <si>
+    <t>Modelar uma Cadeia de Markov como um sistema dinâmico.</t>
+  </si>
+  <si>
+    <t>avancado/autovetores.ipynb</t>
+  </si>
+  <si>
+    <t>Teste 3</t>
+  </si>
+  <si>
+    <t>Modelos de Linguagem</t>
+  </si>
+  <si>
+    <t>Usar a Cadeia de Markov como um modelo de linguagem.</t>
+  </si>
+  <si>
+    <t>avancado/atividade_autovetores.ipynb</t>
+  </si>
+  <si>
+    <t>Regressão e pseudo-inversa.</t>
+  </si>
+  <si>
+    <t>Aplicar a pseudo-inversa para resolver o problema de mínimos quadrados.</t>
+  </si>
+  <si>
+    <t>avancado/regressao.ipynb</t>
+  </si>
+  <si>
+    <t>Estimação da gravidade</t>
+  </si>
+  <si>
+    <t>Estimar um fenômeno físico usando medidas reais e regressão.</t>
+  </si>
+  <si>
+    <t>avancado/gravidade.ipynb</t>
+  </si>
+  <si>
+    <t>Teste 4</t>
+  </si>
+  <si>
+    <t>Compressão sem Perdas</t>
+  </si>
+  <si>
+    <t>Representar números usando menos bits</t>
+  </si>
+  <si>
+    <t>compressao/compressao_huffman.md</t>
+  </si>
+  <si>
+    <t>Compressão com perdas</t>
+  </si>
+  <si>
+    <t>Eliminar informação menos relevante para aumentar a taxa de compressão.</t>
+  </si>
+  <si>
+    <t>Aula-estúdio</t>
+  </si>
+  <si>
+    <t>Avaliação Final</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -138,32 +333,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="7">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -174,10 +372,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -215,71 +413,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -307,7 +505,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -330,11 +528,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -343,13 +541,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -359,7 +557,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -368,7 +566,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -377,7 +575,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -385,10 +583,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -453,77 +651,520 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:D38"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="6" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="3" width="42.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="3" width="55.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="3" width="45.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="2" t="s">
-        <v>9</v>
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+      <c r="A1" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="3">
-        <v>25568.87553523148</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="4">
-        <v>46239</v>
-      </c>
-      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="5">
+        <v>25568.875535243056</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="5">
+        <v>25568.875535266205</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="3">
-        <v>46251</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="3">
-        <v>46253</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" s="3">
-        <v>46254</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
+      <c r="C3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="5">
+        <v>25568.875535277777</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="5">
+        <v>25568.875535324074</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="5">
+        <v>25568.875535347222</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="5">
+        <v>25568.875535358795</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="5">
+        <v>25568.87553540509</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="5">
+        <v>25568.87553542824</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="5">
+        <v>25568.875535439816</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="5">
+        <v>25568.87553548611</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="5">
+        <v>25568.875535509258</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="5">
+        <v>25568.875535520834</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="5">
+        <v>25568.87553556713</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+      <c r="A15" s="5">
+        <v>25568.87553559028</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+      <c r="A16" s="5">
+        <v>25568.875535601852</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="5">
+        <v>25568.87553564815</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+      <c r="A18" s="5">
+        <v>25568.875535671297</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+      <c r="A19" s="5">
+        <v>25568.87553568287</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+      <c r="A20" s="5">
+        <v>25568.875535729167</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+      <c r="A21" s="5">
+        <v>25568.875535810184</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+      <c r="A22" s="5">
+        <v>25568.875535833333</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+      <c r="A23" s="5">
+        <v>25568.87553584491</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+      <c r="A24" s="5">
+        <v>25568.875535891202</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+      <c r="A25" s="5">
+        <v>25568.87553591435</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+      <c r="A26" s="5">
+        <v>25568.875535925927</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+      <c r="A27" s="5">
+        <v>25568.875535972224</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+      <c r="A28" s="5">
+        <v>25568.875536006944</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+      <c r="A29" s="5">
+        <v>25568.87553605324</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D29" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+      <c r="A30" s="5">
+        <v>25568.87553607639</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+      <c r="A31" s="5">
+        <v>25568.875536087962</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D31" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+      <c r="A32" s="5">
+        <v>25568.87553613426</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D32" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+      <c r="A33" s="5">
+        <v>25568.875536157408</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D33" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+      <c r="A34" s="5">
+        <v>25568.87553616898</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D34" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+      <c r="A35" s="5">
+        <v>25568.875536215277</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D35" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+      <c r="A36" s="5">
+        <v>25568.875536238425</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D36" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+      <c r="A37" s="5">
+        <v>25568.87553625</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D37" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+      <c r="A38" s="5">
+        <v>25568.875536296295</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D38" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -531,61 +1172,80 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:A14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="90" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="3" width="90.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="3" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="2" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/courseware/calendario.xlsx
+++ b/courseware/calendario.xlsx
@@ -98,13 +98,13 @@
     <t>Numpy.</t>
   </si>
   <si>
-    <t>Usar Numpy para representar vetores e suas</t>
+    <t>Usar Numpy para representar vetores e suas operações</t>
   </si>
   <si>
     <t>vetores/numpy01.ipynb</t>
   </si>
   <si>
-    <t>Numpy como ferramenta para visualizar</t>
+    <t>Numpy como ferramenta.</t>
   </si>
   <si>
     <t>Aplicar Numpy e álgebra vetorial para simular uma situação-problema.</t>
@@ -122,7 +122,7 @@
     <t>vetores/projecoes.ipynb</t>
   </si>
   <si>
-    <t>Embeddings</t>
+    <t>Embeddings.</t>
   </si>
   <si>
     <t>Aplicar Numpy para visualizar espaços de embeddings e suas propriedades.</t>
@@ -158,7 +158,7 @@
     <t>matrizes/inversa.md</t>
   </si>
   <si>
-    <t>Determinantes</t>
+    <t>Determinantes.</t>
   </si>
   <si>
     <t>Determinar se um sistema linear tem solução ou não.</t>
@@ -167,7 +167,7 @@
     <t>matrizes/determinante.md</t>
   </si>
   <si>
-    <t>Transformações afins</t>
+    <t>Transformações afins.</t>
   </si>
   <si>
     <t>Relacionar sistemas lineares com transformações geométricas.</t>
